--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_ADO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_ADO.xlsx
@@ -422,23 +422,394 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>height_cm</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>bpg</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>ADO_L._AYERS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>L. Ayers</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>26.3</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ADO_D._CAMBRIDGE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>D. Cambridge</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>12.5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ADO_R._SOEIRO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>R. Soeiro</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>21.7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ADO_R._WOODS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>R. Woods</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ADO_L._BOYLE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L. Boyle</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>20.5</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ADO_J._WOOD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>J. Wood</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>20.3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>9.5</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -484,11 +855,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -546,32 +917,66 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>shooting</t>
+          <t>rotation</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>most_used_zone</t>
+          <t>most_used_player</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>L. Ayers</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>scoring</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>primary_scorer</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>L. Ayers</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>shooting</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>most_used_zone</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>shooting</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>best_zone</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Mid-Range</t>
         </is>
@@ -632,16 +1037,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="C2" t="n">
-        <v>76.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.8</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="3">
@@ -651,16 +1056,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>125.9</v>
+        <v>110.7</v>
       </c>
       <c r="C3" t="n">
-        <v>110.4</v>
+        <v>106.2</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>15.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="4">
@@ -670,16 +1075,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.2</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>110.4</v>
+        <v>106.6</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8</v>
+        <v>-10.8</v>
       </c>
     </row>
     <row r="5">
@@ -689,16 +1094,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.7</v>
+        <v>14.8</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>13.7</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="6">
@@ -708,16 +1113,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>17.2</v>
+        <v>16.8</v>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>11.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="7">
@@ -727,16 +1132,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C7" t="n">
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -749,7 +1154,7 @@
         <v>0.4</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
@@ -765,16 +1170,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>24.5</v>
       </c>
       <c r="C9" t="n">
-        <v>21.3</v>
+        <v>20.8</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
@@ -790,7 +1195,7 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>-0</v>
@@ -853,7 +1258,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Below-average pace; they are more comfortable when the game stays organized in the half court.</t>
+          <t>Above-average pace; expect a game that can speed up if you allow early flow.</t>
         </is>
       </c>
     </row>
@@ -889,7 +1294,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Better-than-average ball security; they do not hand away many live possessions.</t>
+          <t>Loose enough with the ball to be pressured; there are possessions to steal here.</t>
         </is>
       </c>
     </row>
@@ -928,7 +1333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -955,7 +1360,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Control the rhythm: they are more comfortable in a controlled half-court game, so do not let them play cleanly into structure.</t>
+          <t>Set the tempo early: if you let them run into flow, the game can speed up on their terms.</t>
         </is>
       </c>
     </row>
@@ -980,6 +1385,18 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>Stay connected to spacing: their perimeter volume can bend the floor if your help and recovery are sloppy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Game Plan Keys</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Know the first reference: L. Ayers is a primary scorer, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -994,7 +1411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1016,48 +1433,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Perimeter Shooting</t>
+          <t>Offense</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from J. Wood and M. Monteiro; contest, but do not over-help into secondary advantages.</t>
+          <t>The main offensive references are L. Ayers and D. Cambridge; load the scouting plan into those names first.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
+          <t>Priority closeouts start with L. Ayers and J. Wood; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Scoring Areas</t>
+          <t>Perimeter Shooting</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially L. Ayers, D. Cambridge, and J. Palm; force them away from preferred areas.</t>
+          <t>Some perimeter volume comes from M. Monteiro and T. Pinto; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Scoring Areas</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Their offense naturally flows toward Above the Break 3; protect that area early in possessions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Scoring Areas</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Several players have clear comfort zones, especially D. Cambridge, L. Ayers, and J. Silva; force them away from preferred areas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Defensive Emphasis</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Second-chance threat; the first stop is not enough against this team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Do not lose L. Ayers and J. Wood in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1072,23 +1525,274 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>main_zone</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>role_note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>ADO_L._AYERS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>L. Ayers</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>primary scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ADO_D._CAMBRIDGE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>D. Cambridge</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>paint finisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ADO_R._SOEIRO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>R. Soeiro</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ADO_R._WOODS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>R. Woods</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ADO_L._BOYLE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L. Boyle</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ADO_J._WOOD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>J. Wood</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>rotation piece</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1197,34 +1901,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADO_J._WOOD</t>
+          <t>ADO_L._AYERS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>L. Ayers</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H2" t="n">
         <v>1.2</v>
@@ -1243,37 +1947,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADO_M._MONTEIRO</t>
+          <t>ADO_J._WOOD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -1294,32 +1998,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADO_T._PINTO</t>
+          <t>ADO_M._MONTEIRO</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>T. Pinto</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1335,38 +2039,48 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ADO_T._PINTO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>T. Pinto</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>31</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>54.8%</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>43.7%</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1384,23 +2098,23 @@
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>33.6%</t>
         </is>
       </c>
     </row>
@@ -1420,23 +2134,23 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
     </row>
@@ -1456,23 +2170,23 @@
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>12.6%</t>
         </is>
       </c>
     </row>
@@ -1492,42 +2206,34 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>9.1%</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ADO_L._AYERS</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>L. Ayers</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -1536,23 +2242,23 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>7.0%</t>
         </is>
       </c>
     </row>
@@ -1584,11 +2290,11 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -1596,7 +2302,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>61.9%</t>
         </is>
       </c>
     </row>
@@ -1608,12 +2314,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ADO_J._PALM</t>
+          <t>ADO_L._AYERS</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>J. Palm</t>
+          <t>L. Ayers</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1624,23 +2330,23 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>34.4%</t>
         </is>
       </c>
     </row>
@@ -1652,12 +2358,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ADO_R._WOODS</t>
+          <t>ADO_J._SILVA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>J. Silva</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1668,23 +2374,243 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ADO_N._MORAIS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>N. Morais</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="K14" t="n">
+        <v>7</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ADO_R._WOODS</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>R. Woods</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ADO_J._PALM</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>J. Palm</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ADO_L._BOYLE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>L. Boyle</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ADO_M._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>M. Monteiro</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>5</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="M13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>71.4%</t>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>33.3%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_ADO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_ADO.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -515,31 +515,31 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7</t>
         </is>
       </c>
     </row>
@@ -567,7 +567,7 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -576,12 +576,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -591,17 +591,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7</t>
         </is>
       </c>
     </row>
@@ -619,88 +619,88 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADO_R._WOODS</t>
+          <t>ADO_M._MONTEIRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -712,47 +712,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADO_L._BOYLE</t>
+          <t>ADO_R._WOODS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Boyle</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>7.3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -775,41 +775,249 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>19.3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3.7</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ADO_L._BOYLE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>L. Boyle</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2.7</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ADO_N._MORAIS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N. Morais</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>17.0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ADO_J._PALM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J. Palm</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>20.3</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>23.6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ADO_J._SILVA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J. Silva</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>20.1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0.5</t>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -824,24 +1032,82 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>tipo</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>L. Ayers | R. Soeiro</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -978,7 +1244,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Restricted Area</t>
         </is>
       </c>
     </row>
@@ -1037,16 +1303,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.5</v>
+        <v>78.3</v>
       </c>
       <c r="C2" t="n">
-        <v>78.7</v>
+        <v>78.8</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="3">
@@ -1056,13 +1322,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>110.7</v>
+        <v>110</v>
       </c>
       <c r="C3" t="n">
-        <v>106.2</v>
+        <v>105.6</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>4.4</v>
@@ -1078,13 +1344,13 @@
         <v>95.90000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6</v>
+        <v>105.9</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>-10.8</v>
+        <v>-10.1</v>
       </c>
     </row>
     <row r="5">
@@ -1094,16 +1360,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.8</v>
+        <v>14.1</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>15.2</v>
+        <v>14.4</v>
       </c>
     </row>
     <row r="6">
@@ -1113,16 +1379,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>20.7</v>
       </c>
       <c r="C6" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>6.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -1138,10 +1404,10 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="8">
@@ -1157,10 +1423,10 @@
         <v>0.3</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -1170,16 +1436,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.5</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
@@ -1195,7 +1461,7 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>-0</v>
@@ -1208,16 +1474,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C11" t="n">
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1258,7 +1524,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Above-average pace; expect a game that can speed up if you allow early flow.</t>
+          <t>League-average pace; rhythm control matters more than pure speed against them.</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1560,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Loose enough with the ball to be pressured; there are possessions to steal here.</t>
+          <t>Turnover profile is close to league average; pressure helps, but it is not the whole plan.</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1626,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Set the tempo early: if you let them run into flow, the game can speed up on their terms.</t>
+          <t>Own the rhythm: pace itself is not the main separator, so the quality of possessions matters more than speed.</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1450,7 +1716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with L. Ayers and J. Wood; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with L. Ayers, J. Wood, and R. Woods; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1728,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from M. Monteiro and T. Pinto; contest, but do not over-help into secondary advantages.</t>
+          <t>Some perimeter volume comes from L. Boyle and M. Monteiro; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1493,12 +1759,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Defensive Emphasis</t>
+          <t>Units</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Second-chance threat; the first stop is not enough against this team.</t>
+          <t>Recognize the main duo/trio combinations: L. Ayers | R. Soeiro.</t>
         </is>
       </c>
     </row>
@@ -1509,6 +1775,18 @@
         </is>
       </c>
       <c r="B8" t="inlineStr">
+        <is>
+          <t>Second-chance threat; the first stop is not enough against this team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Defensive Emphasis</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Do not lose L. Ayers and J. Wood in help-and-recover situations.</t>
         </is>
@@ -1592,17 +1870,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="D2" t="n">
-        <v>24.5</v>
+        <v>22</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1631,14 +1909,14 @@
         <v>23.7</v>
       </c>
       <c r="D3" t="n">
-        <v>12.5</v>
+        <v>11.3</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1664,17 +1942,17 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.7</v>
+        <v>20.1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1691,26 +1969,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADO_R._WOODS</t>
+          <t>ADO_M._MONTEIRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1727,26 +2005,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADO_L._BOYLE</t>
+          <t>ADO_R._WOODS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Boyle</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.5</v>
+        <v>19.8</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1772,17 +2050,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.3</v>
+        <v>19.3</v>
       </c>
       <c r="D7" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1792,7 +2070,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
@@ -1807,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
@@ -1915,23 +2193,23 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -1961,20 +2239,20 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H3" t="n">
         <v>1.1</v>
@@ -1993,37 +2271,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADO_M._MONTEIRO</t>
+          <t>ADO_R._WOODS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2039,37 +2317,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Volume but lower efficiency</t>
+          <t>Priority closeouts</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADO_T._PINTO</t>
+          <t>ADO_N._MORAIS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>T. Pinto</t>
+          <t>N. Morais</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2085,146 +2363,186 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ADO_L._BOYLE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>L. Boyle</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>16</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>48</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>45.8%</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>33.6%</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>45</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>53.3%</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>31.5%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ADO_M._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>M. Monteiro</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>18</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>27.8%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>12.6%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ADO_D._CAMBRIDGE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>D. Cambridge</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Team zones</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>13</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>23.1%</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>9.1%</t>
-        </is>
-      </c>
+          <t>Volume but lower efficiency</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ADO_T._PINTO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>T. Pinto</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2242,42 +2560,34 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ADO_D._CAMBRIDGE</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>D. Cambridge</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -2290,11 +2600,11 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="M11" t="n">
@@ -2302,26 +2612,18 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>ADO_L._AYERS</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>L. Ayers</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
@@ -2330,42 +2632,34 @@
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>17.4%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ADO_J._SILVA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>J. Silva</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
@@ -2374,42 +2668,34 @@
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Preferred finishing / shooting area</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ADO_N._MORAIS</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>N. Morais</t>
-        </is>
-      </c>
+          <t>Team zones</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
@@ -2418,23 +2704,23 @@
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>6.8%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2732,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ADO_R._WOODS</t>
+          <t>ADO_D._CAMBRIDGE</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>D. Cambridge</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2462,23 +2748,23 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -2490,12 +2776,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ADO_J._PALM</t>
+          <t>ADO_L._AYERS</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>J. Palm</t>
+          <t>L. Ayers</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2506,11 +2792,11 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -2518,11 +2804,11 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>31.1%</t>
         </is>
       </c>
     </row>
@@ -2534,12 +2820,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ADO_L._BOYLE</t>
+          <t>ADO_J._SILVA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>L. Boyle</t>
+          <t>J. Silva</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2550,23 +2836,23 @@
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>76.5%</t>
         </is>
       </c>
     </row>
@@ -2578,12 +2864,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ADO_M._MONTEIRO</t>
+          <t>ADO_N._MORAIS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>N. Morais</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2598,19 +2884,195 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>78.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ADO_J._PALM</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>J. Palm</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>11</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>72.7%</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>68.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ADO_L._BOYLE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>L. Boyle</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>9</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>56.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ADO_R._WOODS</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>R. Woods</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>9</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Preferred finishing / shooting area</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ADO_M._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>M. Monteiro</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>8</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>32.0%</t>
         </is>
       </c>
     </row>

--- a/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_ADO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/opponent_game_plan_packs/opponent_game_plan_ADO.xlsx
@@ -515,31 +515,31 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -567,93 +567,93 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>25.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADO_R._SOEIRO</t>
+          <t>ADO_J._WOOD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R. Soeiro</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -671,36 +671,36 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -723,36 +723,36 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -764,52 +764,52 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADO_J._WOOD</t>
+          <t>ADO_R._SOEIRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>R. Soeiro</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
     </row>
@@ -827,36 +827,36 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -868,12 +868,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADO_N._MORAIS</t>
+          <t>ADO_J._PALM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>N. Morais</t>
+          <t>J. Palm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -883,32 +883,32 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>21.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>6.7</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -920,104 +920,104 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ADO_J._PALM</t>
+          <t>ADO_J._SILVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Palm</t>
+          <t>J. Silva</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>23.6</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>1.7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>1.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ADO_J._SILVA</t>
+          <t>ADO_N._MORAIS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Silva</t>
+          <t>N. Morais</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -1094,20 +1094,107 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>L. Ayers | R. Soeiro</t>
+          <t>D. Cambridge | L. Ayers</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>46.1</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>77.3</v>
+        <v>81.2</v>
       </c>
       <c r="F2" t="n">
-        <v>69.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="G2" t="n">
-        <v>7.8</v>
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>trio</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Most used</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>D. Cambridge | J. Wood | L. Ayers</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="E3" t="n">
+        <v>70</v>
+      </c>
+      <c r="F3" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-6.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>L. Ayers | L. Boyle</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>duo</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Best net</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>L. Ayers | L. Boyle</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>32.8</v>
       </c>
     </row>
   </sheetData>
@@ -1303,16 +1390,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78.3</v>
+        <v>78.5</v>
       </c>
       <c r="C2" t="n">
-        <v>78.8</v>
+        <v>79.3</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="3">
@@ -1322,16 +1409,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>110</v>
+        <v>104.6</v>
       </c>
       <c r="C3" t="n">
-        <v>105.6</v>
+        <v>103.9</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
@@ -1341,16 +1428,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>95.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>105.9</v>
+        <v>104</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>-10.1</v>
+        <v>-9.699999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -1360,16 +1447,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.1</v>
+        <v>10.2</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>14.4</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="6">
@@ -1379,16 +1466,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.7</v>
+        <v>19.5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1404,10 +1491,10 @@
         <v>0.2</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1426,7 +1513,7 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1436,16 +1523,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
         <v>20.7</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="10">
@@ -1461,7 +1548,7 @@
         <v>0.3</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>-0</v>
@@ -1480,7 +1567,7 @@
         <v>0.4</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1584,7 +1671,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Above-average three-point volume; spacing discipline and clean closeouts matter.</t>
+          <t>Perimeter volume is close to league average; shot mix alone does not define them.</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1737,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stay connected to spacing: their perimeter volume can bend the floor if your help and recovery are sloppy.</t>
+          <t>Know the first reference: L. Ayers is a spot-up shooter, and the plan should start with taking away his comfort.</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1749,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Know the first reference: L. Ayers is a primary scorer, and the plan should start with taking away his comfort.</t>
+          <t>Closeout discipline matters: L. Ayers, R. Woods are the first perimeter names you cannot lose in help situations.</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1803,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priority closeouts start with L. Ayers, J. Wood, and R. Woods; do not lose them in help-and-recover situations.</t>
+          <t>Priority closeouts start with L. Ayers, R. Woods, and N. Morais; do not lose them in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1815,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Some perimeter volume comes from L. Boyle and M. Monteiro; contest, but do not over-help into secondary advantages.</t>
+          <t>Some perimeter volume comes from J. Wood and L. Boyle; contest, but do not over-help into secondary advantages.</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1839,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Several players have clear comfort zones, especially D. Cambridge, L. Ayers, and J. Silva; force them away from preferred areas.</t>
+          <t>Several players have clear comfort zones, especially L. Ayers, J. Silva, and D. Cambridge; force them away from preferred areas.</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1851,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Recognize the main duo/trio combinations: L. Ayers | R. Soeiro.</t>
+          <t>Recognize the main duo/trio combinations: D. Cambridge | L. Ayers and D. Cambridge | J. Wood | L. Ayers.</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1875,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Do not lose L. Ayers and J. Wood in help-and-recover situations.</t>
+          <t>Do not lose L. Ayers and R. Woods in help-and-recover situations.</t>
         </is>
       </c>
     </row>
@@ -1813,7 +1900,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1870,17 +1957,17 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.3</v>
+        <v>28.8</v>
       </c>
       <c r="D2" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1890,7 +1977,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>primary scorer</t>
+          <t>spot-up shooter</t>
         </is>
       </c>
     </row>
@@ -1906,17 +1993,17 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23.7</v>
+        <v>25.6</v>
       </c>
       <c r="D3" t="n">
-        <v>11.3</v>
+        <v>10.5</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1933,26 +2020,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADO_R._SOEIRO</t>
+          <t>ADO_J._WOOD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R. Soeiro</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1962,7 +2049,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
@@ -1978,17 +2065,17 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="D5" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1998,7 +2085,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
@@ -2014,17 +2101,17 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2034,33 +2121,33 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>rotation piece</t>
+          <t>bench spacer</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADO_J._WOOD</t>
+          <t>ADO_R._SOEIRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>R. Soeiro</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.3</v>
+        <v>17.3</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="E7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2193,20 +2280,20 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="H2" t="n">
         <v>1.1</v>
@@ -2230,29 +2317,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ADO_J._WOOD</t>
+          <t>ADO_R._WOODS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
         <v>1.1</v>
@@ -2276,12 +2363,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ADO_R._WOODS</t>
+          <t>ADO_N._MORAIS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>N. Morais</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -2294,14 +2381,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -2322,32 +2409,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADO_N._MORAIS</t>
+          <t>ADO_R._SOEIRO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>N. Morais</t>
+          <t>R. Soeiro</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -2368,32 +2455,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADO_L._BOYLE</t>
+          <t>ADO_J._WOOD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>L. Boyle</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -2414,29 +2501,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADO_M._MONTEIRO</t>
+          <t>ADO_L._BOYLE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>L. Boyle</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="H7" t="n">
         <v>0.7</v>
@@ -2469,23 +2556,23 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -2506,32 +2593,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ADO_T._PINTO</t>
+          <t>ADO_M._MONTEIRO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>T. Pinto</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -2564,11 +2651,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -2576,7 +2663,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
     </row>
@@ -2600,19 +2687,19 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>29.9%</t>
         </is>
       </c>
     </row>
@@ -2636,11 +2723,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -2648,7 +2735,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
     </row>
@@ -2672,19 +2759,19 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -2708,19 +2795,19 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.5%</t>
         </is>
       </c>
     </row>
@@ -2732,12 +2819,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ADO_D._CAMBRIDGE</t>
+          <t>ADO_L._AYERS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>D. Cambridge</t>
+          <t>L. Ayers</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -2748,23 +2835,23 @@
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>30.6%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2863,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ADO_L._AYERS</t>
+          <t>ADO_J._SILVA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L. Ayers</t>
+          <t>J. Silva</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -2792,23 +2879,23 @@
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>81.0%</t>
         </is>
       </c>
     </row>
@@ -2820,12 +2907,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ADO_J._SILVA</t>
+          <t>ADO_D._CAMBRIDGE</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>J. Silva</t>
+          <t>D. Cambridge</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -2840,19 +2927,19 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2864,12 +2951,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ADO_N._MORAIS</t>
+          <t>ADO_J._PALM</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>N. Morais</t>
+          <t>J. Palm</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2880,23 +2967,23 @@
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>68.4%</t>
         </is>
       </c>
     </row>
@@ -2908,12 +2995,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ADO_J._PALM</t>
+          <t>ADO_N._MORAIS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>J. Palm</t>
+          <t>N. Morais</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2924,7 +3011,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2932,15 +3019,15 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -2972,19 +3059,19 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>57.9%</t>
         </is>
       </c>
     </row>
@@ -2996,12 +3083,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ADO_R._WOODS</t>
+          <t>ADO_M._MONTEIRO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -3016,19 +3103,19 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
     </row>
@@ -3040,12 +3127,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ADO_M._MONTEIRO</t>
+          <t>ADO_R._WOODS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -3060,19 +3147,19 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
     </row>
